--- a/Biblioteca de Soporte/1. ELICITACION/1.6 Backlog/BL_V1.0.3.xlsx
+++ b/Biblioteca de Soporte/1. ELICITACION/1.6 Backlog/BL_V1.0.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\22426_G2_ADS\PREGAME\4. TERCERA ITERACION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\6TO SEMESTRE\ANALISIS Y DISEÑO DE SOFTWARE\PRIMER PARCIAL\22426_G2_ADS\Biblioteca de Soporte\1. ELICITACION\1.6 Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CA36095-9F83-48C4-B9AC-BEF8422F2BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20027174-464B-47E4-84A0-7FD097BB2E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="190">
   <si>
     <t>ID</t>
   </si>
@@ -338,21 +338,6 @@
     <t>REQ009-1</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">CONCLUSION: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Se evidenció que el tiempo estimado fue poco realista, ya que disminuyó hasta valores negativos, mientras que el tiempo real se mantuvo siempre positivo</t>
-    </r>
-  </si>
-  <si>
     <t>Dia 6</t>
   </si>
   <si>
@@ -627,9 +612,6 @@
   </si>
   <si>
     <t>Diseñar de la interfaz para la generación de reportes por Materia Prima</t>
-  </si>
-  <si>
-    <t>RECOMENDACION:Se podria recomendar ajustar los tiempo estimados aunque se puede ver que al final de cuentas quedo mas en lo que real posible sin ningun retraso</t>
   </si>
 </sst>
 </file>
@@ -1207,18 +1189,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1324,6 +1294,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1915,6 +1897,92 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>772438</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>208767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>532357</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>2567835</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectángulo 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D24063-43FE-D6A9-87EC-F1CE2EF1C4FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3308959" y="12901808"/>
+          <a:ext cx="8684713" cy="2359068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1100"/>
+            <a:t>Conclusion:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-ES"/>
+            <a:t>La comparación entre el tiempo real y el tiempo estimado revela una ligera desviación durante las primeras etapas del proyecto, donde el tiempo real fue mayor al previsto, lo que podría indicar una planificación inicial optimista o imprevistos en la ejecución. Sin embargo, a medida que avanza el proyecto, se observa una tendencia de convergencia entre ambos tiempos, demostrando una mejora en la eficiencia y en el control del desarrollo. Esta evolución sugiere que el equipo logró adaptarse a las exigencias del proyecto, alineando progresivamente la ejecución con la planificación establecida.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-ES"/>
+          </a:br>
+          <a:br>
+            <a:rPr lang="es-ES"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-ES"/>
+            <a:t>Recomendacion:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="es-ES"/>
+            <a:t>Se recomienda reforzar la fase de planificación y análisis inicial, incorporando márgenes de contingencia más realistas y una estimación más detallada por tareas. </a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2136,19 +2204,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J995"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
     <col min="6" max="6" width="60" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="11" customWidth="1"/>
-    <col min="9" max="27" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="11" customWidth="1"/>
+    <col min="9" max="27" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2158,7 +2226,7 @@
       <c r="H1" s="35"/>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="26" t="s">
         <v>0</v>
@@ -2186,21 +2254,21 @@
       </c>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="28" t="s">
         <v>9</v>
@@ -2226,7 +2294,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="28" t="s">
         <v>16</v>
@@ -2252,7 +2320,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="28" t="s">
         <v>20</v>
@@ -2278,7 +2346,7 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="28" t="s">
         <v>23</v>
@@ -2304,7 +2372,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="29" t="s">
         <v>26</v>
@@ -2330,21 +2398,21 @@
       </c>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="63"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="101"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="29" t="s">
         <v>31</v>
@@ -2370,7 +2438,7 @@
       </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="29" t="s">
         <v>34</v>
@@ -2396,7 +2464,7 @@
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="29" t="s">
         <v>37</v>
@@ -2422,27 +2490,27 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="63"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="101"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>11</v>
@@ -2451,7 +2519,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="29"/>
       <c r="H14" s="33" t="s">
@@ -2462,13 +2530,13 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="29" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>11</v>
@@ -2477,7 +2545,7 @@
         <v>18</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G15" s="29"/>
       <c r="H15" s="33" t="s">
@@ -2488,13 +2556,13 @@
       </c>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>11</v>
@@ -2503,7 +2571,7 @@
         <v>18</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G16" s="29"/>
       <c r="H16" s="34" t="s">
@@ -2514,21 +2582,21 @@
       </c>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="61" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="63"/>
-    </row>
-    <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="101"/>
+    </row>
+    <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>42</v>
@@ -2550,9 +2618,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C19" s="29" t="s">
         <v>45</v>
@@ -2574,982 +2642,982 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:I3"/>
@@ -3569,20 +3637,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B1:I816"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.42578125" customWidth="1"/>
+    <col min="1" max="2" width="12.44140625" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" customWidth="1"/>
-    <col min="6" max="6" width="56.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="26" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" customWidth="1"/>
+    <col min="6" max="6" width="56.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="26" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -3608,24 +3676,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
       <c r="E4" s="49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F4" s="48"/>
       <c r="G4" s="48"/>
       <c r="H4" s="48"/>
       <c r="I4" s="48"/>
     </row>
-    <row r="5" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>11</v>
@@ -3644,7 +3712,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>54</v>
@@ -3660,12 +3728,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="42"/>
@@ -3678,12 +3746,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42"/>
@@ -3696,12 +3764,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="42"/>
@@ -3714,12 +3782,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3732,7 +3800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -3742,12 +3810,12 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="36" t="s">
         <v>119</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>120</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>11</v>
@@ -3766,7 +3834,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39"/>
       <c r="C13" s="40" t="s">
         <v>54</v>
@@ -3782,12 +3850,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="41" t="s">
         <v>66</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42"/>
@@ -3800,12 +3868,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" s="39"/>
       <c r="E15" s="39"/>
@@ -3818,12 +3886,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="41" t="s">
         <v>68</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -3836,7 +3904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41"/>
       <c r="C17" s="39"/>
       <c r="D17" s="42"/>
@@ -3846,21 +3914,21 @@
       <c r="H17" s="42"/>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" spans="2:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B18" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>124</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>125</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="36" t="s">
         <v>126</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>127</v>
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="36" t="s">
@@ -3870,7 +3938,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B19" s="39"/>
       <c r="C19" s="40" t="s">
         <v>54</v>
@@ -3886,12 +3954,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41" t="s">
         <v>69</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="39"/>
       <c r="E20" s="39"/>
@@ -3904,12 +3972,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D21" s="39"/>
       <c r="E21" s="39"/>
@@ -3922,12 +3990,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41" t="s">
         <v>71</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -3940,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41"/>
       <c r="C23" s="39"/>
       <c r="D23" s="42"/>
@@ -3950,21 +4018,21 @@
       <c r="H23" s="42"/>
       <c r="I23" s="39"/>
     </row>
-    <row r="24" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="36" t="s">
         <v>131</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>132</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="36" t="s">
         <v>133</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>134</v>
       </c>
       <c r="G24" s="37"/>
       <c r="H24" s="36" t="s">
@@ -3974,7 +4042,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
       <c r="C25" s="40" t="s">
         <v>54</v>
@@ -3990,12 +4058,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="25" t="s">
         <v>72</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
         <v>58</v>
@@ -4004,12 +4072,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="25" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G27" t="s">
         <v>60</v>
@@ -4018,7 +4086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4028,21 +4096,21 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>138</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="46" t="s">
         <v>139</v>
-      </c>
-      <c r="F29" s="46" t="s">
-        <v>140</v>
       </c>
       <c r="G29" s="37"/>
       <c r="H29" s="36" t="s">
@@ -4052,7 +4120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
       <c r="C30" s="40" t="s">
         <v>54</v>
@@ -4068,15 +4136,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="25" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
         <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>142</v>
       </c>
       <c r="G31" t="s">
         <v>58</v>
@@ -4085,12 +4153,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="25" t="s">
         <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
         <v>60</v>
@@ -4099,24 +4167,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="48"/>
       <c r="C33" s="48"/>
       <c r="D33" s="48"/>
       <c r="E33" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F33" s="48"/>
       <c r="G33" s="48"/>
       <c r="H33" s="48"/>
       <c r="I33" s="48"/>
     </row>
-    <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>11</v>
@@ -4135,7 +4203,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="3" t="s">
         <v>54</v>
@@ -4151,12 +4219,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36" s="42"/>
       <c r="E36" s="42"/>
@@ -4169,12 +4237,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D37" s="42"/>
       <c r="E37" s="42"/>
@@ -4187,12 +4255,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" s="42"/>
       <c r="E38" s="42"/>
@@ -4205,12 +4273,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" s="42"/>
       <c r="E39" s="42"/>
@@ -4223,12 +4291,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -4241,7 +4309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -4251,12 +4319,12 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="36" t="s">
         <v>151</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>152</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>11</v>
@@ -4275,7 +4343,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="39"/>
       <c r="C43" s="40" t="s">
         <v>54</v>
@@ -4291,12 +4359,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41" t="s">
         <v>86</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D44" s="42"/>
       <c r="E44" s="42"/>
@@ -4309,12 +4377,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D45" s="42"/>
       <c r="E45" s="42"/>
@@ -4327,7 +4395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41"/>
       <c r="C46" s="39"/>
       <c r="D46" s="42"/>
@@ -4337,21 +4405,21 @@
       <c r="H46" s="42"/>
       <c r="I46" s="39"/>
     </row>
-    <row r="47" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" s="38" t="s">
         <v>155</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>156</v>
       </c>
       <c r="D47" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E47" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F47" s="36" t="s">
         <v>126</v>
-      </c>
-      <c r="F47" s="36" t="s">
-        <v>127</v>
       </c>
       <c r="G47" s="37"/>
       <c r="H47" s="36" t="s">
@@ -4361,7 +4429,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="39"/>
       <c r="C48" s="40" t="s">
         <v>54</v>
@@ -4377,12 +4445,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41" t="s">
         <v>88</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D49" s="39"/>
       <c r="E49" s="39"/>
@@ -4395,12 +4463,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41" t="s">
         <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D50" s="39"/>
       <c r="E50" s="39"/>
@@ -4413,24 +4481,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="48"/>
       <c r="C51" s="48"/>
       <c r="D51" s="48"/>
       <c r="E51" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F51" s="48"/>
       <c r="G51" s="48"/>
       <c r="H51" s="48"/>
       <c r="I51" s="48"/>
     </row>
-    <row r="52" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>11</v>
@@ -4449,7 +4517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="3" t="s">
         <v>54</v>
@@ -4465,12 +4533,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="42"/>
@@ -4483,12 +4551,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="42"/>
@@ -4501,12 +4569,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C56" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="42"/>
@@ -4519,12 +4587,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -4537,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="5"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -4547,12 +4615,12 @@
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>11</v>
@@ -4571,7 +4639,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="39"/>
       <c r="C60" s="40" t="s">
         <v>54</v>
@@ -4587,12 +4655,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41" t="s">
         <v>91</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
@@ -4605,12 +4673,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41" t="s">
         <v>92</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D62" s="42"/>
       <c r="E62" s="42"/>
@@ -4623,7 +4691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41"/>
       <c r="C63" s="39"/>
       <c r="D63" s="42"/>
@@ -4633,21 +4701,21 @@
       <c r="H63" s="42"/>
       <c r="I63" s="39"/>
     </row>
-    <row r="64" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D64" s="36" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" s="36" t="s">
         <v>126</v>
-      </c>
-      <c r="F64" s="36" t="s">
-        <v>127</v>
       </c>
       <c r="G64" s="37"/>
       <c r="H64" s="36" t="s">
@@ -4657,7 +4725,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="39"/>
       <c r="C65" s="40" t="s">
         <v>54</v>
@@ -4673,12 +4741,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C66" s="43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D66" s="39"/>
       <c r="E66" s="39"/>
@@ -4691,12 +4759,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D67" s="39"/>
       <c r="E67" s="39"/>
@@ -4709,21 +4777,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="48"/>
       <c r="C68" s="48"/>
       <c r="D68" s="48"/>
       <c r="E68" s="49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F68" s="48"/>
       <c r="G68" s="48"/>
       <c r="H68" s="48"/>
       <c r="I68" s="48"/>
     </row>
-    <row r="69" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>42</v>
@@ -4745,7 +4813,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="3" t="s">
         <v>54</v>
@@ -4761,12 +4829,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B71" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C71" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D71" s="42"/>
       <c r="E71" s="42"/>
@@ -4779,12 +4847,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -4797,7 +4865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="5"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -4807,9 +4875,9 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
     </row>
-    <row r="74" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C74" s="36" t="s">
         <v>45</v>
@@ -4831,7 +4899,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="39"/>
       <c r="C75" s="40" t="s">
         <v>54</v>
@@ -4847,12 +4915,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D76" s="42"/>
       <c r="E76" s="42"/>
@@ -4865,12 +4933,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C77" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D77" s="42"/>
       <c r="E77" s="42"/>
@@ -4883,745 +4951,745 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5635,22 +5703,22 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X1022"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.140625" customWidth="1"/>
-    <col min="24" max="40" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.109375" customWidth="1"/>
+    <col min="24" max="40" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -5674,148 +5742,148 @@
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="65" t="s">
+      <c r="D3" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="E3" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="F3" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="G3" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="66" t="s">
+      <c r="H3" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="66" t="s">
+      <c r="I3" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="J3" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="66" t="s">
+      <c r="K3" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="M3" s="67" t="s">
+      <c r="L3" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="N3" s="67" t="s">
+      <c r="M3" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="67" t="s">
+      <c r="N3" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="P3" s="67" t="s">
+      <c r="O3" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="Q3" s="67" t="s">
+      <c r="P3" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="R3" s="68" t="s">
+      <c r="Q3" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="R3" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="68" t="s">
+      <c r="S3" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="T3" s="68" t="s">
+      <c r="T3" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="68" t="s">
+      <c r="U3" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="W3" s="69" t="s">
+      <c r="W3" s="65" t="s">
         <v>82</v>
       </c>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="69">
         <v>2</v>
       </c>
-      <c r="D4" s="74">
-        <v>0</v>
-      </c>
-      <c r="E4" s="74">
-        <v>0</v>
-      </c>
-      <c r="F4" s="74">
-        <v>0</v>
-      </c>
-      <c r="G4" s="74">
-        <v>0</v>
-      </c>
-      <c r="H4" s="75">
-        <v>0</v>
-      </c>
-      <c r="I4" s="75">
-        <v>0</v>
-      </c>
-      <c r="J4" s="75">
-        <v>0</v>
-      </c>
-      <c r="K4" s="75">
-        <v>0</v>
-      </c>
-      <c r="L4" s="75">
-        <v>0</v>
-      </c>
-      <c r="M4" s="76">
-        <v>0</v>
-      </c>
-      <c r="N4" s="76">
-        <v>0</v>
-      </c>
-      <c r="O4" s="76">
-        <v>0</v>
-      </c>
-      <c r="P4" s="76">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="76">
-        <v>0</v>
-      </c>
-      <c r="R4" s="77">
-        <v>0</v>
-      </c>
-      <c r="S4" s="77">
-        <v>0</v>
-      </c>
-      <c r="T4" s="77">
-        <v>1</v>
-      </c>
-      <c r="U4" s="77">
-        <v>0</v>
-      </c>
-      <c r="V4" s="77">
-        <v>1</v>
-      </c>
-      <c r="W4" s="78">
+      <c r="D4" s="70">
+        <v>0</v>
+      </c>
+      <c r="E4" s="70">
+        <v>0</v>
+      </c>
+      <c r="F4" s="70">
+        <v>0</v>
+      </c>
+      <c r="G4" s="70">
+        <v>0</v>
+      </c>
+      <c r="H4" s="71">
+        <v>0</v>
+      </c>
+      <c r="I4" s="71">
+        <v>0</v>
+      </c>
+      <c r="J4" s="71">
+        <v>0</v>
+      </c>
+      <c r="K4" s="71">
+        <v>0</v>
+      </c>
+      <c r="L4" s="71">
+        <v>0</v>
+      </c>
+      <c r="M4" s="72">
+        <v>0</v>
+      </c>
+      <c r="N4" s="72">
+        <v>0</v>
+      </c>
+      <c r="O4" s="72">
+        <v>0</v>
+      </c>
+      <c r="P4" s="72">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="72">
+        <v>0</v>
+      </c>
+      <c r="R4" s="73">
+        <v>0</v>
+      </c>
+      <c r="S4" s="73">
+        <v>0</v>
+      </c>
+      <c r="T4" s="73">
+        <v>1</v>
+      </c>
+      <c r="U4" s="73">
+        <v>0</v>
+      </c>
+      <c r="V4" s="73">
+        <v>1</v>
+      </c>
+      <c r="W4" s="74">
         <f>SUM(R4:V4)</f>
         <v>2</v>
       </c>
       <c r="X4" s="9"/>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="18" t="s">
         <v>59</v>
@@ -5886,7 +5954,7 @@
       </c>
       <c r="X5" s="9"/>
     </row>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="18" t="s">
         <v>61</v>
@@ -5957,7 +6025,7 @@
       </c>
       <c r="X6" s="9"/>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="18" t="s">
         <v>62</v>
@@ -6028,7 +6096,7 @@
       </c>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="18" t="s">
         <v>66</v>
@@ -6097,7 +6165,7 @@
       </c>
       <c r="X8" s="9"/>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="18" t="s">
         <v>67</v>
@@ -6168,7 +6236,7 @@
       </c>
       <c r="X9" s="9"/>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="18" t="s">
         <v>68</v>
@@ -6239,7 +6307,7 @@
       </c>
       <c r="X10" s="9"/>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="18" t="s">
         <v>69</v>
@@ -6310,7 +6378,7 @@
       </c>
       <c r="X11" s="9"/>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="18" t="s">
         <v>70</v>
@@ -6381,7 +6449,7 @@
       </c>
       <c r="X12" s="9"/>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="18" t="s">
         <v>71</v>
@@ -6452,7 +6520,7 @@
       </c>
       <c r="X13" s="9"/>
     </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="18" t="s">
         <v>72</v>
@@ -6523,7 +6591,7 @@
       </c>
       <c r="X14" s="9"/>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="18" t="s">
         <v>73</v>
@@ -6594,7 +6662,7 @@
       </c>
       <c r="X15" s="9"/>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="18" t="s">
         <v>74</v>
@@ -6665,149 +6733,149 @@
       </c>
       <c r="X16" s="9"/>
     </row>
-    <row r="17" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="80">
-        <v>1</v>
-      </c>
-      <c r="D17" s="81">
-        <v>0</v>
-      </c>
-      <c r="E17" s="81">
-        <v>0</v>
-      </c>
-      <c r="F17" s="81">
-        <v>0</v>
-      </c>
-      <c r="G17" s="81">
-        <v>0</v>
-      </c>
-      <c r="H17" s="82">
-        <v>0</v>
-      </c>
-      <c r="I17" s="82">
-        <v>0</v>
-      </c>
-      <c r="J17" s="82">
-        <v>0</v>
-      </c>
-      <c r="K17" s="82">
-        <v>0</v>
-      </c>
-      <c r="L17" s="82">
-        <v>0</v>
-      </c>
-      <c r="M17" s="83">
-        <v>0</v>
-      </c>
-      <c r="N17" s="83">
-        <v>0</v>
-      </c>
-      <c r="O17" s="83">
-        <v>0</v>
-      </c>
-      <c r="P17" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="83">
-        <v>0</v>
-      </c>
-      <c r="R17" s="84">
-        <v>0</v>
-      </c>
-      <c r="S17" s="84">
-        <v>1</v>
-      </c>
-      <c r="T17" s="84">
-        <v>0</v>
-      </c>
-      <c r="U17" s="84">
-        <v>0</v>
-      </c>
-      <c r="V17" s="84">
-        <v>0</v>
-      </c>
-      <c r="W17" s="85">
+      <c r="C17" s="76">
+        <v>1</v>
+      </c>
+      <c r="D17" s="77">
+        <v>0</v>
+      </c>
+      <c r="E17" s="77">
+        <v>0</v>
+      </c>
+      <c r="F17" s="77">
+        <v>0</v>
+      </c>
+      <c r="G17" s="77">
+        <v>0</v>
+      </c>
+      <c r="H17" s="78">
+        <v>0</v>
+      </c>
+      <c r="I17" s="78">
+        <v>0</v>
+      </c>
+      <c r="J17" s="78">
+        <v>0</v>
+      </c>
+      <c r="K17" s="78">
+        <v>0</v>
+      </c>
+      <c r="L17" s="78">
+        <v>0</v>
+      </c>
+      <c r="M17" s="79">
+        <v>0</v>
+      </c>
+      <c r="N17" s="79">
+        <v>0</v>
+      </c>
+      <c r="O17" s="79">
+        <v>0</v>
+      </c>
+      <c r="P17" s="79">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="79">
+        <v>0</v>
+      </c>
+      <c r="R17" s="80">
+        <v>0</v>
+      </c>
+      <c r="S17" s="80">
+        <v>1</v>
+      </c>
+      <c r="T17" s="80">
+        <v>0</v>
+      </c>
+      <c r="U17" s="80">
+        <v>0</v>
+      </c>
+      <c r="V17" s="80">
+        <v>0</v>
+      </c>
+      <c r="W17" s="81">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="87">
+      <c r="C18" s="83">
         <v>2</v>
       </c>
-      <c r="D18" s="88">
-        <v>0</v>
-      </c>
-      <c r="E18" s="88">
-        <v>0</v>
-      </c>
-      <c r="F18" s="88">
-        <v>0</v>
-      </c>
-      <c r="G18" s="88">
-        <v>0</v>
-      </c>
-      <c r="H18" s="89">
-        <v>0</v>
-      </c>
-      <c r="I18" s="89">
-        <v>0</v>
-      </c>
-      <c r="J18" s="89">
-        <v>0</v>
-      </c>
-      <c r="K18" s="89">
-        <v>0</v>
-      </c>
-      <c r="L18" s="89">
-        <v>0</v>
-      </c>
-      <c r="M18" s="76">
-        <v>0</v>
-      </c>
-      <c r="N18" s="76">
-        <v>0</v>
-      </c>
-      <c r="O18" s="76">
-        <v>0</v>
-      </c>
-      <c r="P18" s="76">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="76">
-        <v>1</v>
-      </c>
-      <c r="R18" s="90">
-        <v>0</v>
-      </c>
-      <c r="S18" s="90">
-        <v>0</v>
-      </c>
-      <c r="T18" s="90">
-        <v>0</v>
-      </c>
-      <c r="U18" s="90">
-        <v>0</v>
-      </c>
-      <c r="V18" s="90">
-        <v>0</v>
-      </c>
-      <c r="W18" s="78">
+      <c r="D18" s="84">
+        <v>0</v>
+      </c>
+      <c r="E18" s="84">
+        <v>0</v>
+      </c>
+      <c r="F18" s="84">
+        <v>0</v>
+      </c>
+      <c r="G18" s="84">
+        <v>0</v>
+      </c>
+      <c r="H18" s="85">
+        <v>0</v>
+      </c>
+      <c r="I18" s="85">
+        <v>0</v>
+      </c>
+      <c r="J18" s="85">
+        <v>0</v>
+      </c>
+      <c r="K18" s="85">
+        <v>0</v>
+      </c>
+      <c r="L18" s="85">
+        <v>0</v>
+      </c>
+      <c r="M18" s="72">
+        <v>0</v>
+      </c>
+      <c r="N18" s="72">
+        <v>0</v>
+      </c>
+      <c r="O18" s="72">
+        <v>0</v>
+      </c>
+      <c r="P18" s="72">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="72">
+        <v>1</v>
+      </c>
+      <c r="R18" s="86">
+        <v>0</v>
+      </c>
+      <c r="S18" s="86">
+        <v>0</v>
+      </c>
+      <c r="T18" s="86">
+        <v>0</v>
+      </c>
+      <c r="U18" s="86">
+        <v>0</v>
+      </c>
+      <c r="V18" s="86">
+        <v>0</v>
+      </c>
+      <c r="W18" s="74">
         <f>SUM(M18:Q18)</f>
         <v>2</v>
       </c>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="18" t="s">
         <v>83</v>
@@ -6878,7 +6946,7 @@
       </c>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="18" t="s">
         <v>84</v>
@@ -6949,7 +7017,7 @@
       </c>
       <c r="X20" s="9"/>
     </row>
-    <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="18" t="s">
         <v>85</v>
@@ -7020,10 +7088,10 @@
       </c>
       <c r="X21" s="9"/>
     </row>
-    <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C22" s="17">
         <v>1</v>
@@ -7091,7 +7159,7 @@
       </c>
       <c r="X22" s="9"/>
     </row>
-    <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="18" t="s">
         <v>86</v>
@@ -7162,7 +7230,7 @@
       </c>
       <c r="X23" s="9"/>
     </row>
-    <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="18" t="s">
         <v>87</v>
@@ -7233,7 +7301,7 @@
       </c>
       <c r="X24" s="9"/>
     </row>
-    <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="18" t="s">
         <v>88</v>
@@ -7304,33 +7372,33 @@
       </c>
       <c r="X25" s="9"/>
     </row>
-    <row r="26" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="91">
-        <v>1</v>
-      </c>
-      <c r="D26" s="92">
-        <v>0</v>
-      </c>
-      <c r="E26" s="92">
-        <v>0</v>
-      </c>
-      <c r="F26" s="92">
-        <v>0</v>
-      </c>
-      <c r="G26" s="92">
-        <v>0</v>
-      </c>
-      <c r="H26" s="93">
-        <v>0</v>
-      </c>
-      <c r="I26" s="94">
-        <v>0</v>
-      </c>
-      <c r="J26" s="94">
+      <c r="C26" s="87">
+        <v>1</v>
+      </c>
+      <c r="D26" s="88">
+        <v>0</v>
+      </c>
+      <c r="E26" s="88">
+        <v>0</v>
+      </c>
+      <c r="F26" s="88">
+        <v>0</v>
+      </c>
+      <c r="G26" s="88">
+        <v>0</v>
+      </c>
+      <c r="H26" s="89">
+        <v>0</v>
+      </c>
+      <c r="I26" s="90">
+        <v>0</v>
+      </c>
+      <c r="J26" s="90">
         <v>0</v>
       </c>
       <c r="K26" s="57">
@@ -7339,114 +7407,114 @@
       <c r="L26" s="57">
         <v>0</v>
       </c>
-      <c r="M26" s="95">
-        <v>1</v>
-      </c>
-      <c r="N26" s="95">
-        <v>0</v>
-      </c>
-      <c r="O26" s="95">
-        <v>0</v>
-      </c>
-      <c r="P26" s="95">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="95">
-        <v>0</v>
-      </c>
-      <c r="R26" s="96">
-        <v>0</v>
-      </c>
-      <c r="S26" s="96">
-        <v>0</v>
-      </c>
-      <c r="T26" s="96">
-        <v>0</v>
-      </c>
-      <c r="U26" s="96">
-        <v>0</v>
-      </c>
-      <c r="V26" s="96">
-        <v>0</v>
-      </c>
-      <c r="W26" s="85">
+      <c r="M26" s="91">
+        <v>1</v>
+      </c>
+      <c r="N26" s="91">
+        <v>0</v>
+      </c>
+      <c r="O26" s="91">
+        <v>0</v>
+      </c>
+      <c r="P26" s="91">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="91">
+        <v>0</v>
+      </c>
+      <c r="R26" s="92">
+        <v>0</v>
+      </c>
+      <c r="S26" s="92">
+        <v>0</v>
+      </c>
+      <c r="T26" s="92">
+        <v>0</v>
+      </c>
+      <c r="U26" s="92">
+        <v>0</v>
+      </c>
+      <c r="V26" s="92">
+        <v>0</v>
+      </c>
+      <c r="W26" s="81">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="X26" s="9"/>
     </row>
-    <row r="27" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="98">
+      <c r="C27" s="94">
         <v>2</v>
       </c>
-      <c r="D27" s="74">
-        <v>0</v>
-      </c>
-      <c r="E27" s="74">
-        <v>0</v>
-      </c>
-      <c r="F27" s="74">
-        <v>0</v>
-      </c>
-      <c r="G27" s="74">
-        <v>0</v>
-      </c>
-      <c r="H27" s="77">
-        <v>0</v>
-      </c>
-      <c r="I27" s="77">
-        <v>0</v>
-      </c>
-      <c r="J27" s="77">
-        <v>0</v>
-      </c>
-      <c r="K27" s="77">
-        <v>1</v>
-      </c>
-      <c r="L27" s="77">
-        <v>1</v>
-      </c>
-      <c r="M27" s="99">
-        <v>0</v>
-      </c>
-      <c r="N27" s="99">
-        <v>0</v>
-      </c>
-      <c r="O27" s="99">
-        <v>0</v>
-      </c>
-      <c r="P27" s="99">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="99">
-        <v>0</v>
-      </c>
-      <c r="R27" s="100">
-        <v>0</v>
-      </c>
-      <c r="S27" s="100">
-        <v>0</v>
-      </c>
-      <c r="T27" s="100">
-        <v>0</v>
-      </c>
-      <c r="U27" s="100">
-        <v>0</v>
-      </c>
-      <c r="V27" s="96">
-        <v>0</v>
-      </c>
-      <c r="W27" s="78">
+      <c r="D27" s="70">
+        <v>0</v>
+      </c>
+      <c r="E27" s="70">
+        <v>0</v>
+      </c>
+      <c r="F27" s="70">
+        <v>0</v>
+      </c>
+      <c r="G27" s="70">
+        <v>0</v>
+      </c>
+      <c r="H27" s="73">
+        <v>0</v>
+      </c>
+      <c r="I27" s="73">
+        <v>0</v>
+      </c>
+      <c r="J27" s="73">
+        <v>0</v>
+      </c>
+      <c r="K27" s="73">
+        <v>1</v>
+      </c>
+      <c r="L27" s="73">
+        <v>1</v>
+      </c>
+      <c r="M27" s="95">
+        <v>0</v>
+      </c>
+      <c r="N27" s="95">
+        <v>0</v>
+      </c>
+      <c r="O27" s="95">
+        <v>0</v>
+      </c>
+      <c r="P27" s="95">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="95">
+        <v>0</v>
+      </c>
+      <c r="R27" s="96">
+        <v>0</v>
+      </c>
+      <c r="S27" s="96">
+        <v>0</v>
+      </c>
+      <c r="T27" s="96">
+        <v>0</v>
+      </c>
+      <c r="U27" s="96">
+        <v>0</v>
+      </c>
+      <c r="V27" s="92">
+        <v>0</v>
+      </c>
+      <c r="W27" s="74">
         <f>SUM(H27:L27)</f>
         <v>2</v>
       </c>
       <c r="X27" s="9"/>
     </row>
-    <row r="28" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="18" t="s">
         <v>90</v>
@@ -7466,19 +7534,19 @@
       <c r="G28" s="13">
         <v>0</v>
       </c>
-      <c r="H28" s="77">
-        <v>0</v>
-      </c>
-      <c r="I28" s="77">
-        <v>0</v>
-      </c>
-      <c r="J28" s="77">
+      <c r="H28" s="73">
+        <v>0</v>
+      </c>
+      <c r="I28" s="73">
+        <v>0</v>
+      </c>
+      <c r="J28" s="73">
         <v>1</v>
       </c>
       <c r="K28" s="50">
         <v>1</v>
       </c>
-      <c r="L28" s="75">
+      <c r="L28" s="71">
         <v>0</v>
       </c>
       <c r="M28" s="55">
@@ -7508,19 +7576,19 @@
       <c r="U28" s="52">
         <v>0</v>
       </c>
-      <c r="V28" s="96">
+      <c r="V28" s="92">
         <v>0</v>
       </c>
       <c r="W28" s="19">
-        <f t="shared" ref="W28:W34" si="2">SUM(H28:L28)</f>
+        <f t="shared" ref="W28:W33" si="2">SUM(H28:L28)</f>
         <v>2</v>
       </c>
       <c r="X28" s="9"/>
     </row>
-    <row r="29" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" s="17">
         <v>1</v>
@@ -7537,19 +7605,19 @@
       <c r="G29" s="16">
         <v>0</v>
       </c>
-      <c r="H29" s="77">
-        <v>0</v>
-      </c>
-      <c r="I29" s="77">
-        <v>0</v>
-      </c>
-      <c r="J29" s="77">
-        <v>1</v>
-      </c>
-      <c r="K29" s="75">
-        <v>0</v>
-      </c>
-      <c r="L29" s="75">
+      <c r="H29" s="73">
+        <v>0</v>
+      </c>
+      <c r="I29" s="73">
+        <v>0</v>
+      </c>
+      <c r="J29" s="73">
+        <v>1</v>
+      </c>
+      <c r="K29" s="71">
+        <v>0</v>
+      </c>
+      <c r="L29" s="71">
         <v>0</v>
       </c>
       <c r="M29" s="55">
@@ -7579,7 +7647,7 @@
       <c r="U29" s="52">
         <v>0</v>
       </c>
-      <c r="V29" s="96">
+      <c r="V29" s="92">
         <v>0</v>
       </c>
       <c r="W29" s="19">
@@ -7588,39 +7656,39 @@
       </c>
       <c r="X29" s="9"/>
     </row>
-    <row r="30" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="17">
         <v>1</v>
       </c>
-      <c r="D30" s="74">
-        <v>0</v>
-      </c>
-      <c r="E30" s="74">
-        <v>0</v>
-      </c>
-      <c r="F30" s="74">
-        <v>0</v>
-      </c>
-      <c r="G30" s="74">
-        <v>0</v>
-      </c>
-      <c r="H30" s="77">
-        <v>0</v>
-      </c>
-      <c r="I30" s="77">
-        <v>1</v>
-      </c>
-      <c r="J30" s="77">
-        <v>0</v>
-      </c>
-      <c r="K30" s="75">
-        <v>0</v>
-      </c>
-      <c r="L30" s="75">
+      <c r="D30" s="70">
+        <v>0</v>
+      </c>
+      <c r="E30" s="70">
+        <v>0</v>
+      </c>
+      <c r="F30" s="70">
+        <v>0</v>
+      </c>
+      <c r="G30" s="70">
+        <v>0</v>
+      </c>
+      <c r="H30" s="73">
+        <v>0</v>
+      </c>
+      <c r="I30" s="73">
+        <v>1</v>
+      </c>
+      <c r="J30" s="73">
+        <v>0</v>
+      </c>
+      <c r="K30" s="71">
+        <v>0</v>
+      </c>
+      <c r="L30" s="71">
         <v>0</v>
       </c>
       <c r="M30" s="55">
@@ -7650,7 +7718,7 @@
       <c r="U30" s="52">
         <v>0</v>
       </c>
-      <c r="V30" s="96">
+      <c r="V30" s="92">
         <v>0</v>
       </c>
       <c r="W30" s="19">
@@ -7659,7 +7727,7 @@
       </c>
       <c r="X30" s="9"/>
     </row>
-    <row r="31" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="18" t="s">
         <v>91</v>
@@ -7679,19 +7747,19 @@
       <c r="G31" s="13">
         <v>0</v>
       </c>
-      <c r="H31" s="77">
-        <v>0</v>
-      </c>
-      <c r="I31" s="77">
-        <v>0</v>
-      </c>
-      <c r="J31" s="77">
-        <v>0</v>
-      </c>
-      <c r="K31" s="75">
-        <v>0</v>
-      </c>
-      <c r="L31" s="75">
+      <c r="H31" s="73">
+        <v>0</v>
+      </c>
+      <c r="I31" s="73">
+        <v>0</v>
+      </c>
+      <c r="J31" s="73">
+        <v>0</v>
+      </c>
+      <c r="K31" s="71">
+        <v>0</v>
+      </c>
+      <c r="L31" s="71">
         <v>1</v>
       </c>
       <c r="M31" s="55">
@@ -7721,7 +7789,7 @@
       <c r="U31" s="52">
         <v>0</v>
       </c>
-      <c r="V31" s="96">
+      <c r="V31" s="92">
         <v>0</v>
       </c>
       <c r="W31" s="19">
@@ -7730,7 +7798,7 @@
       </c>
       <c r="X31" s="9"/>
     </row>
-    <row r="32" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="18" t="s">
         <v>92</v>
@@ -7750,19 +7818,19 @@
       <c r="G32" s="16">
         <v>0</v>
       </c>
-      <c r="H32" s="77">
-        <v>0</v>
-      </c>
-      <c r="I32" s="77">
-        <v>1</v>
-      </c>
-      <c r="J32" s="77">
-        <v>0</v>
-      </c>
-      <c r="K32" s="75">
-        <v>1</v>
-      </c>
-      <c r="L32" s="75">
+      <c r="H32" s="73">
+        <v>0</v>
+      </c>
+      <c r="I32" s="73">
+        <v>1</v>
+      </c>
+      <c r="J32" s="73">
+        <v>0</v>
+      </c>
+      <c r="K32" s="71">
+        <v>1</v>
+      </c>
+      <c r="L32" s="71">
         <v>0</v>
       </c>
       <c r="M32" s="55">
@@ -7792,7 +7860,7 @@
       <c r="U32" s="52">
         <v>0</v>
       </c>
-      <c r="V32" s="96">
+      <c r="V32" s="92">
         <v>0</v>
       </c>
       <c r="W32" s="19">
@@ -7801,39 +7869,39 @@
       </c>
       <c r="X32" s="9"/>
     </row>
-    <row r="33" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="17">
         <v>1</v>
       </c>
-      <c r="D33" s="74">
-        <v>0</v>
-      </c>
-      <c r="E33" s="74">
-        <v>0</v>
-      </c>
-      <c r="F33" s="74">
-        <v>0</v>
-      </c>
-      <c r="G33" s="74">
-        <v>0</v>
-      </c>
-      <c r="H33" s="77">
-        <v>0</v>
-      </c>
-      <c r="I33" s="101">
-        <v>0</v>
-      </c>
-      <c r="J33" s="77">
-        <v>0</v>
-      </c>
-      <c r="K33" s="77">
-        <v>0</v>
-      </c>
-      <c r="L33" s="75">
+      <c r="D33" s="70">
+        <v>0</v>
+      </c>
+      <c r="E33" s="70">
+        <v>0</v>
+      </c>
+      <c r="F33" s="70">
+        <v>0</v>
+      </c>
+      <c r="G33" s="70">
+        <v>0</v>
+      </c>
+      <c r="H33" s="73">
+        <v>0</v>
+      </c>
+      <c r="I33" s="97">
+        <v>0</v>
+      </c>
+      <c r="J33" s="73">
+        <v>0</v>
+      </c>
+      <c r="K33" s="73">
+        <v>0</v>
+      </c>
+      <c r="L33" s="71">
         <v>1</v>
       </c>
       <c r="M33" s="55">
@@ -7863,7 +7931,7 @@
       <c r="U33" s="52">
         <v>0</v>
       </c>
-      <c r="V33" s="96">
+      <c r="V33" s="92">
         <v>0</v>
       </c>
       <c r="W33" s="19">
@@ -7872,54 +7940,54 @@
       </c>
       <c r="X33" s="9"/>
     </row>
-    <row r="34" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
-      <c r="B34" s="79" t="s">
-        <v>178</v>
-      </c>
-      <c r="C34" s="91">
+      <c r="B34" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="87">
         <v>2</v>
       </c>
       <c r="D34" s="13">
         <v>0</v>
       </c>
-      <c r="E34" s="74">
-        <v>0</v>
-      </c>
-      <c r="F34" s="74">
+      <c r="E34" s="70">
+        <v>0</v>
+      </c>
+      <c r="F34" s="70">
         <v>0</v>
       </c>
       <c r="G34" s="13">
         <v>0</v>
       </c>
-      <c r="H34" s="77">
-        <v>1</v>
-      </c>
-      <c r="I34" s="75">
-        <v>1</v>
-      </c>
-      <c r="J34" s="77">
-        <v>0</v>
-      </c>
-      <c r="K34" s="77">
-        <v>0</v>
-      </c>
-      <c r="L34" s="75">
-        <v>0</v>
-      </c>
-      <c r="M34" s="99">
-        <v>0</v>
-      </c>
-      <c r="N34" s="99">
-        <v>0</v>
-      </c>
-      <c r="O34" s="99">
-        <v>0</v>
-      </c>
-      <c r="P34" s="99">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="99">
+      <c r="H34" s="73">
+        <v>1</v>
+      </c>
+      <c r="I34" s="71">
+        <v>1</v>
+      </c>
+      <c r="J34" s="73">
+        <v>0</v>
+      </c>
+      <c r="K34" s="73">
+        <v>0</v>
+      </c>
+      <c r="L34" s="71">
+        <v>0</v>
+      </c>
+      <c r="M34" s="95">
+        <v>0</v>
+      </c>
+      <c r="N34" s="95">
+        <v>0</v>
+      </c>
+      <c r="O34" s="95">
+        <v>0</v>
+      </c>
+      <c r="P34" s="95">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="95">
         <v>0</v>
       </c>
       <c r="R34" s="52">
@@ -7934,48 +8002,48 @@
       <c r="U34" s="52">
         <v>0</v>
       </c>
-      <c r="V34" s="96">
-        <v>0</v>
-      </c>
-      <c r="W34" s="85">
+      <c r="V34" s="92">
+        <v>0</v>
+      </c>
+      <c r="W34" s="81">
         <f>SUM(H34:L34)</f>
         <v>2</v>
       </c>
       <c r="X34" s="9"/>
     </row>
-    <row r="35" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
-      <c r="B35" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="86">
-        <v>1</v>
-      </c>
-      <c r="D35" s="97">
-        <v>0</v>
-      </c>
-      <c r="E35" s="74">
-        <v>0</v>
-      </c>
-      <c r="F35" s="74">
-        <v>0</v>
-      </c>
-      <c r="G35" s="97">
-        <v>1</v>
-      </c>
-      <c r="H35" s="77">
-        <v>0</v>
-      </c>
-      <c r="I35" s="77">
-        <v>0</v>
-      </c>
-      <c r="J35" s="77">
-        <v>0</v>
-      </c>
-      <c r="K35" s="77">
-        <v>0</v>
-      </c>
-      <c r="L35" s="77">
+      <c r="B35" s="66" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="82">
+        <v>1</v>
+      </c>
+      <c r="D35" s="93">
+        <v>0</v>
+      </c>
+      <c r="E35" s="70">
+        <v>0</v>
+      </c>
+      <c r="F35" s="70">
+        <v>0</v>
+      </c>
+      <c r="G35" s="93">
+        <v>1</v>
+      </c>
+      <c r="H35" s="73">
+        <v>0</v>
+      </c>
+      <c r="I35" s="73">
+        <v>0</v>
+      </c>
+      <c r="J35" s="73">
+        <v>0</v>
+      </c>
+      <c r="K35" s="73">
+        <v>0</v>
+      </c>
+      <c r="L35" s="73">
         <v>0</v>
       </c>
       <c r="M35" s="55">
@@ -7993,31 +8061,31 @@
       <c r="Q35" s="55">
         <v>0</v>
       </c>
-      <c r="R35" s="77">
-        <v>0</v>
-      </c>
-      <c r="S35" s="77">
-        <v>0</v>
-      </c>
-      <c r="T35" s="77">
-        <v>0</v>
-      </c>
-      <c r="U35" s="77">
-        <v>0</v>
-      </c>
-      <c r="V35" s="96">
-        <v>0</v>
-      </c>
-      <c r="W35" s="71">
+      <c r="R35" s="73">
+        <v>0</v>
+      </c>
+      <c r="S35" s="73">
+        <v>0</v>
+      </c>
+      <c r="T35" s="73">
+        <v>0</v>
+      </c>
+      <c r="U35" s="73">
+        <v>0</v>
+      </c>
+      <c r="V35" s="92">
+        <v>0</v>
+      </c>
+      <c r="W35" s="67">
         <f>SUM(D35:G35)</f>
         <v>1</v>
       </c>
       <c r="X35" s="9"/>
     </row>
-    <row r="36" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C36" s="17">
         <v>2</v>
@@ -8034,19 +8102,19 @@
       <c r="G36" s="16">
         <v>0</v>
       </c>
-      <c r="H36" s="77">
-        <v>0</v>
-      </c>
-      <c r="I36" s="77">
-        <v>0</v>
-      </c>
-      <c r="J36" s="77">
-        <v>0</v>
-      </c>
-      <c r="K36" s="77">
-        <v>0</v>
-      </c>
-      <c r="L36" s="77">
+      <c r="H36" s="73">
+        <v>0</v>
+      </c>
+      <c r="I36" s="73">
+        <v>0</v>
+      </c>
+      <c r="J36" s="73">
+        <v>0</v>
+      </c>
+      <c r="K36" s="73">
+        <v>0</v>
+      </c>
+      <c r="L36" s="73">
         <v>0</v>
       </c>
       <c r="M36" s="55">
@@ -8064,19 +8132,19 @@
       <c r="Q36" s="55">
         <v>0</v>
       </c>
-      <c r="R36" s="77">
-        <v>0</v>
-      </c>
-      <c r="S36" s="77">
-        <v>0</v>
-      </c>
-      <c r="T36" s="77">
-        <v>0</v>
-      </c>
-      <c r="U36" s="77">
-        <v>0</v>
-      </c>
-      <c r="V36" s="96">
+      <c r="R36" s="73">
+        <v>0</v>
+      </c>
+      <c r="S36" s="73">
+        <v>0</v>
+      </c>
+      <c r="T36" s="73">
+        <v>0</v>
+      </c>
+      <c r="U36" s="73">
+        <v>0</v>
+      </c>
+      <c r="V36" s="92">
         <v>0</v>
       </c>
       <c r="W36" s="19">
@@ -8085,10 +8153,10 @@
       </c>
       <c r="X36" s="9"/>
     </row>
-    <row r="37" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C37" s="17">
         <v>1</v>
@@ -8105,19 +8173,19 @@
       <c r="G37" s="16">
         <v>1</v>
       </c>
-      <c r="H37" s="77">
-        <v>0</v>
-      </c>
-      <c r="I37" s="77">
-        <v>0</v>
-      </c>
-      <c r="J37" s="77">
-        <v>0</v>
-      </c>
-      <c r="K37" s="77">
-        <v>0</v>
-      </c>
-      <c r="L37" s="77">
+      <c r="H37" s="73">
+        <v>0</v>
+      </c>
+      <c r="I37" s="73">
+        <v>0</v>
+      </c>
+      <c r="J37" s="73">
+        <v>0</v>
+      </c>
+      <c r="K37" s="73">
+        <v>0</v>
+      </c>
+      <c r="L37" s="73">
         <v>0</v>
       </c>
       <c r="M37" s="55">
@@ -8135,19 +8203,19 @@
       <c r="Q37" s="55">
         <v>0</v>
       </c>
-      <c r="R37" s="77">
-        <v>0</v>
-      </c>
-      <c r="S37" s="77">
-        <v>0</v>
-      </c>
-      <c r="T37" s="77">
-        <v>0</v>
-      </c>
-      <c r="U37" s="77">
-        <v>0</v>
-      </c>
-      <c r="V37" s="96">
+      <c r="R37" s="73">
+        <v>0</v>
+      </c>
+      <c r="S37" s="73">
+        <v>0</v>
+      </c>
+      <c r="T37" s="73">
+        <v>0</v>
+      </c>
+      <c r="U37" s="73">
+        <v>0</v>
+      </c>
+      <c r="V37" s="92">
         <v>0</v>
       </c>
       <c r="W37" s="19">
@@ -8156,10 +8224,10 @@
       </c>
       <c r="X37" s="9"/>
     </row>
-    <row r="38" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
       <c r="B38" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C38" s="17">
         <v>2</v>
@@ -8176,19 +8244,19 @@
       <c r="G38" s="16">
         <v>0</v>
       </c>
-      <c r="H38" s="77">
-        <v>0</v>
-      </c>
-      <c r="I38" s="77">
-        <v>0</v>
-      </c>
-      <c r="J38" s="77">
-        <v>0</v>
-      </c>
-      <c r="K38" s="77">
-        <v>0</v>
-      </c>
-      <c r="L38" s="77">
+      <c r="H38" s="73">
+        <v>0</v>
+      </c>
+      <c r="I38" s="73">
+        <v>0</v>
+      </c>
+      <c r="J38" s="73">
+        <v>0</v>
+      </c>
+      <c r="K38" s="73">
+        <v>0</v>
+      </c>
+      <c r="L38" s="73">
         <v>0</v>
       </c>
       <c r="M38" s="55">
@@ -8206,19 +8274,19 @@
       <c r="Q38" s="55">
         <v>0</v>
       </c>
-      <c r="R38" s="77">
-        <v>0</v>
-      </c>
-      <c r="S38" s="77">
-        <v>0</v>
-      </c>
-      <c r="T38" s="77">
-        <v>0</v>
-      </c>
-      <c r="U38" s="77">
-        <v>0</v>
-      </c>
-      <c r="V38" s="77">
+      <c r="R38" s="73">
+        <v>0</v>
+      </c>
+      <c r="S38" s="73">
+        <v>0</v>
+      </c>
+      <c r="T38" s="73">
+        <v>0</v>
+      </c>
+      <c r="U38" s="73">
+        <v>0</v>
+      </c>
+      <c r="V38" s="73">
         <v>0</v>
       </c>
       <c r="W38" s="19">
@@ -8227,7 +8295,7 @@
       </c>
       <c r="X38" s="9"/>
     </row>
-    <row r="39" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="20" t="s">
         <v>93</v>
       </c>
@@ -8314,7 +8382,7 @@
       <c r="W39" s="21"/>
       <c r="X39" s="9"/>
     </row>
-    <row r="40" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="22" t="s">
         <v>94</v>
       </c>
@@ -8401,7 +8469,7 @@
       <c r="W40" s="24"/>
       <c r="X40" s="9"/>
     </row>
-    <row r="41" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
@@ -8425,58 +8493,54 @@
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
     </row>
-    <row r="42" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
     </row>
-    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
     </row>
-    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
     </row>
-    <row r="65" spans="1:23" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" ht="162.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
-      <c r="B65" s="58" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="58"/>
+    </row>
+    <row r="66" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
-      <c r="B66" s="59" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:23" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="59"/>
+    </row>
+    <row r="67" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:23" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="59"/>
       <c r="D77" s="59"/>
       <c r="E77" s="59"/>
@@ -8499,7 +8563,7 @@
       <c r="V77" s="59"/>
       <c r="W77" s="59"/>
     </row>
-    <row r="78" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C78" s="59"/>
       <c r="D78" s="59"/>
       <c r="E78" s="59"/>
@@ -8522,7 +8586,7 @@
       <c r="V78" s="59"/>
       <c r="W78" s="59"/>
     </row>
-    <row r="79" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="59"/>
       <c r="C79" s="59"/>
       <c r="D79" s="59"/>
@@ -8546,9 +8610,9 @@
       <c r="V79" s="59"/>
       <c r="W79" s="59"/>
     </row>
-    <row r="80" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="58"/>
       <c r="C82" s="59"/>
       <c r="D82" s="59"/>
@@ -8572,7 +8636,7 @@
       <c r="V82" s="59"/>
       <c r="W82" s="59"/>
     </row>
-    <row r="83" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="59"/>
       <c r="C83" s="59"/>
       <c r="D83" s="59"/>
@@ -8596,7 +8660,7 @@
       <c r="V83" s="59"/>
       <c r="W83" s="59"/>
     </row>
-    <row r="84" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="59"/>
       <c r="C84" s="59"/>
       <c r="D84" s="59"/>
@@ -8620,944 +8684,944 @@
       <c r="V84" s="59"/>
       <c r="W84" s="59"/>
     </row>
-    <row r="85" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1016" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1017" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1018" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1019" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1020" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1021" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1022" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1016" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1017" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1018" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1019" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1020" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1021" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1022" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9570,23 +9634,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100EDB39E34F5A9B445B025C05B2A05D030" ma:contentTypeVersion="13" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="3d104e777bff27600c75745aad47d27e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f1f31ffb-9912-4459-99c8-b26e82094b51" xmlns:ns4="ce621958-37b1-43fe-a1f1-1aad67996a88" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cf3581354608339ee345d673b4b6aec0" ns3:_="" ns4:_="">
     <xsd:import namespace="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
@@ -9805,10 +9852,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3352EB-243F-434C-83F5-25E913689064}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA40288-AE83-4CFD-88FC-2C88A8A97CD6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
+    <ds:schemaRef ds:uri="ce621958-37b1-43fe-a1f1-1aad67996a88"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9831,20 +9906,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA40288-AE83-4CFD-88FC-2C88A8A97CD6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3352EB-243F-434C-83F5-25E913689064}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
-    <ds:schemaRef ds:uri="ce621958-37b1-43fe-a1f1-1aad67996a88"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>